--- a/artfynd/A 38022-2022 artfynd.xlsx
+++ b/artfynd/A 38022-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38022-2022 artfynd.xlsx
+++ b/artfynd/A 38022-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,220 +2545,6 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112607077</v>
-      </c>
-      <c r="B18" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Tvärån, Nb</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>835244</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7383657</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>112607078</v>
-      </c>
-      <c r="B19" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tvärån, Nb</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>835319</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7383631</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
